--- a/artfynd/A 32280-2022 artfynd.xlsx
+++ b/artfynd/A 32280-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32280-2022 artfynd.xlsx
+++ b/artfynd/A 32280-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95195198</v>
+        <v>95820690</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>4740</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392753.288006463</v>
+        <v>392753</v>
       </c>
       <c r="R2" t="n">
-        <v>6502685.843884221</v>
+        <v>6502686</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -753,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95820690</v>
+        <v>95195179</v>
       </c>
       <c r="B3" t="n">
-        <v>90282</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,30 +791,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4740</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392753.288006463</v>
+        <v>392753</v>
       </c>
       <c r="R3" t="n">
-        <v>6502685.843884221</v>
+        <v>6502686</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,22 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>längs vandringsleden (Klevensbergen)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,6 +891,216 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>95820702</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ravelsbergen, Kållandsö, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>392753</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6502686</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Otterstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan-Åke Rosén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan-Åke Rosén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>95195198</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ravelsbergen, Kållandsö, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>392753</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6502686</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Otterstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan-Åke Rosén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan-Åke Rosén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32280-2022 artfynd.xlsx
+++ b/artfynd/A 32280-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95820690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95195179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95820702</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,8 +1121,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95195198</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>